--- a/college-coderank/frontend/public/sample_student_template.xlsx
+++ b/college-coderank/frontend/public/sample_student_template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>name</t>
   </si>
@@ -34,41 +34,53 @@
     <t>leetcodeUsername</t>
   </si>
   <si>
+    <t>codechefUsername</t>
+  </si>
+  <si>
+    <t>geeksforgeeksUsername</t>
+  </si>
+  <si>
     <t>githubUsername</t>
   </si>
   <si>
     <t>hackerrankUsername</t>
   </si>
   <si>
-    <t>Example Student</t>
-  </si>
-  <si>
-    <t>student@college.edu</t>
-  </si>
-  <si>
-    <t>COL-001</t>
-  </si>
-  <si>
-    <t>Computer Science</t>
+    <t>Aarav Sharma</t>
+  </si>
+  <si>
+    <t>aarav.sharma@rungta.ac.in</t>
+  </si>
+  <si>
+    <t>21CS042</t>
+  </si>
+  <si>
+    <t>Computer Science &amp; Engineering</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>leetcode-handle</t>
-  </si>
-  <si>
-    <t>github-handle</t>
-  </si>
-  <si>
-    <t>hackerrank-handle</t>
+    <t>aarav_coder</t>
+  </si>
+  <si>
+    <t>aarav_sharma</t>
+  </si>
+  <si>
+    <t>aarav_sharma21</t>
+  </si>
+  <si>
+    <t>aaravsharma-dev</t>
+  </si>
+  <si>
+    <t>aarav_s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -76,13 +88,22 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED5758"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -97,8 +118,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,65 +460,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="11" width="20" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
